--- a/data/nzd0187/nzd0187.xlsx
+++ b/data/nzd0187/nzd0187.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G418"/>
+  <dimension ref="A1:G419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11664,6 +11664,33 @@
       <c r="G418" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>426</v>
+      </c>
+      <c r="C419" t="n">
+        <v>443.32</v>
+      </c>
+      <c r="D419" t="n">
+        <v>445.47</v>
+      </c>
+      <c r="E419" t="n">
+        <v>442.81</v>
+      </c>
+      <c r="F419" t="n">
+        <v>424.05</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11678,7 +11705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B566"/>
+  <dimension ref="A1:B567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17341,6 +17368,16 @@
       </c>
       <c r="B566" t="n">
         <v>1.59</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -17509,28 +17546,28 @@
         <v>0.0347</v>
       </c>
       <c r="I2" t="n">
-        <v>6.495236304863965</v>
+        <v>6.49562340745432</v>
       </c>
       <c r="J2" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K2" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7906055340819191</v>
+        <v>0.7913831040588951</v>
       </c>
       <c r="M2" t="n">
-        <v>14.9708859933123</v>
+        <v>14.93612576496593</v>
       </c>
       <c r="N2" t="n">
-        <v>602.0971365690848</v>
+        <v>600.6374958042566</v>
       </c>
       <c r="O2" t="n">
-        <v>24.53766770842504</v>
+        <v>24.50790680177025</v>
       </c>
       <c r="P2" t="n">
-        <v>255.1223079569304</v>
+        <v>255.118150486173</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17591,28 +17628,28 @@
         <v>0.0289</v>
       </c>
       <c r="I3" t="n">
-        <v>6.314634203402698</v>
+        <v>6.323926901619851</v>
       </c>
       <c r="J3" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K3" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7191128536536873</v>
+        <v>0.7203920446846862</v>
       </c>
       <c r="M3" t="n">
-        <v>17.79163233629178</v>
+        <v>17.77995013772387</v>
       </c>
       <c r="N3" t="n">
-        <v>833.6127721508907</v>
+        <v>832.6024569599967</v>
       </c>
       <c r="O3" t="n">
-        <v>28.87235307609843</v>
+        <v>28.85485153245459</v>
       </c>
       <c r="P3" t="n">
-        <v>257.5681292394647</v>
+        <v>257.4680428134099</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17673,28 +17710,28 @@
         <v>0.0363</v>
       </c>
       <c r="I4" t="n">
-        <v>5.924149363179544</v>
+        <v>5.934633502369244</v>
       </c>
       <c r="J4" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K4" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8645110786626949</v>
+        <v>0.8649534661645097</v>
       </c>
       <c r="M4" t="n">
-        <v>11.73240116621613</v>
+        <v>11.75803755717538</v>
       </c>
       <c r="N4" t="n">
-        <v>295.4707488280798</v>
+        <v>296.0418699355816</v>
       </c>
       <c r="O4" t="n">
-        <v>17.18926260280178</v>
+        <v>17.20586731134416</v>
       </c>
       <c r="P4" t="n">
-        <v>267.2488061159651</v>
+        <v>267.136122564684</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -17755,28 +17792,28 @@
         <v>0.0335</v>
       </c>
       <c r="I5" t="n">
-        <v>5.318626372274055</v>
+        <v>5.32788697204407</v>
       </c>
       <c r="J5" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K5" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L5" t="n">
-        <v>0.871065635543957</v>
+        <v>0.8714698807868322</v>
       </c>
       <c r="M5" t="n">
-        <v>11.66152707742683</v>
+        <v>11.69045910535014</v>
       </c>
       <c r="N5" t="n">
-        <v>225.5701165782151</v>
+        <v>226.0319688491674</v>
       </c>
       <c r="O5" t="n">
-        <v>15.01899186291194</v>
+        <v>15.0343596088815</v>
       </c>
       <c r="P5" t="n">
-        <v>283.098186256653</v>
+        <v>282.9988250633901</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -17837,28 +17874,28 @@
         <v>0.0432</v>
       </c>
       <c r="I6" t="n">
-        <v>5.226178130341041</v>
+        <v>5.227474548860673</v>
       </c>
       <c r="J6" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K6" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8613534220322097</v>
+        <v>0.8619465413284614</v>
       </c>
       <c r="M6" t="n">
-        <v>12.06617699084163</v>
+        <v>12.04331611113387</v>
       </c>
       <c r="N6" t="n">
-        <v>235.7182153147812</v>
+        <v>235.1573720309312</v>
       </c>
       <c r="O6" t="n">
-        <v>15.3531174461339</v>
+        <v>15.33484176739138</v>
       </c>
       <c r="P6" t="n">
-        <v>284.4067044681043</v>
+        <v>284.3926706346178</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -17900,7 +17937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G418"/>
+  <dimension ref="A1:G419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33249,6 +33286,43 @@
         </is>
       </c>
     </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>-36.98028344097944,174.4685254548975</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>-36.979621666784546,174.46813197509584</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>-36.97892747124533,174.4679040522745</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-36.97822299159466,174.46772862207234</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-36.9774841043854,174.46772889128746</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0187/nzd0187.xlsx
+++ b/data/nzd0187/nzd0187.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G419"/>
+  <dimension ref="A1:G420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11683,7 +11683,7 @@
         <v>445.47</v>
       </c>
       <c r="E419" t="n">
-        <v>442.81</v>
+        <v>440.4</v>
       </c>
       <c r="F419" t="n">
         <v>424.05</v>
@@ -11691,6 +11691,33 @@
       <c r="G419" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>426.96</v>
+      </c>
+      <c r="C420" t="n">
+        <v>444.34</v>
+      </c>
+      <c r="D420" t="n">
+        <v>446.29</v>
+      </c>
+      <c r="E420" t="n">
+        <v>441.4</v>
+      </c>
+      <c r="F420" t="n">
+        <v>426.17</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B567"/>
+  <dimension ref="A1:B568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17378,6 +17405,16 @@
       </c>
       <c r="B567" t="n">
         <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -17546,28 +17583,28 @@
         <v>0.0347</v>
       </c>
       <c r="I2" t="n">
-        <v>6.49562340745432</v>
+        <v>6.496373956177614</v>
       </c>
       <c r="J2" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K2" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7913831040588951</v>
+        <v>0.7921717851845285</v>
       </c>
       <c r="M2" t="n">
-        <v>14.93612576496593</v>
+        <v>14.90300378022683</v>
       </c>
       <c r="N2" t="n">
-        <v>600.6374958042566</v>
+        <v>599.1898323435157</v>
       </c>
       <c r="O2" t="n">
-        <v>24.50790680177025</v>
+        <v>24.47835436346806</v>
       </c>
       <c r="P2" t="n">
-        <v>255.118150486173</v>
+        <v>255.1100808936318</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17628,28 +17665,28 @@
         <v>0.0289</v>
       </c>
       <c r="I3" t="n">
-        <v>6.323926901619851</v>
+        <v>6.333511840228965</v>
       </c>
       <c r="J3" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K3" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7203920446846862</v>
+        <v>0.7216629839987354</v>
       </c>
       <c r="M3" t="n">
-        <v>17.77995013772387</v>
+        <v>17.76982200937825</v>
       </c>
       <c r="N3" t="n">
-        <v>832.6024569599967</v>
+        <v>831.6713100547563</v>
       </c>
       <c r="O3" t="n">
-        <v>28.85485153245459</v>
+        <v>28.83871200408847</v>
       </c>
       <c r="P3" t="n">
-        <v>257.4680428134099</v>
+        <v>257.3646984641229</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17710,28 +17747,28 @@
         <v>0.0363</v>
       </c>
       <c r="I4" t="n">
-        <v>5.934633502369244</v>
+        <v>5.945306047199948</v>
       </c>
       <c r="J4" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K4" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8649534661645097</v>
+        <v>0.8653774536405983</v>
       </c>
       <c r="M4" t="n">
-        <v>11.75803755717538</v>
+        <v>11.78472063871718</v>
       </c>
       <c r="N4" t="n">
-        <v>296.0418699355816</v>
+        <v>296.6696168919463</v>
       </c>
       <c r="O4" t="n">
-        <v>17.20586731134416</v>
+        <v>17.22409988626245</v>
       </c>
       <c r="P4" t="n">
-        <v>267.136122564684</v>
+        <v>267.0212908396149</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -17792,28 +17829,28 @@
         <v>0.0335</v>
       </c>
       <c r="I5" t="n">
-        <v>5.32788697204407</v>
+        <v>5.335270575653115</v>
       </c>
       <c r="J5" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K5" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8714698807868322</v>
+        <v>0.8719798560138493</v>
       </c>
       <c r="M5" t="n">
-        <v>11.69045910535014</v>
+        <v>11.70834497284102</v>
       </c>
       <c r="N5" t="n">
-        <v>226.0319688491674</v>
+        <v>226.1138014451291</v>
       </c>
       <c r="O5" t="n">
-        <v>15.0343596088815</v>
+        <v>15.03708088177786</v>
       </c>
       <c r="P5" t="n">
-        <v>282.9988250633901</v>
+        <v>282.9195050820156</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -17874,28 +17911,28 @@
         <v>0.0432</v>
       </c>
       <c r="I6" t="n">
-        <v>5.227474548860673</v>
+        <v>5.229666433295228</v>
       </c>
       <c r="J6" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K6" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8619465413284614</v>
+        <v>0.8625566045775759</v>
       </c>
       <c r="M6" t="n">
-        <v>12.04331611113387</v>
+        <v>12.02526433159574</v>
       </c>
       <c r="N6" t="n">
-        <v>235.1573720309312</v>
+        <v>234.6364336263315</v>
       </c>
       <c r="O6" t="n">
-        <v>15.33484176739138</v>
+        <v>15.31784689916737</v>
       </c>
       <c r="P6" t="n">
-        <v>284.3926706346178</v>
+        <v>284.3689173329246</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -17937,7 +17974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G419"/>
+  <dimension ref="A1:G420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33309,7 +33346,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>-36.97822299159466,174.46772862207234</t>
+          <t>-36.97821784208694,174.46775492273974</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -33320,6 +33357,43 @@
       <c r="G419" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>-36.980285492289376,174.46851497801904</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>-36.97962384626989,174.46812084349793</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>-36.97892922336772,174.4678951034196</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>-36.97821997881283,174.46774400960018</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-36.977488634248495,174.46770575565438</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0187/nzd0187.xlsx
+++ b/data/nzd0187/nzd0187.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G420"/>
+  <dimension ref="A1:G423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11716,6 +11716,87 @@
         <v>426.17</v>
       </c>
       <c r="G420" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>425.08</v>
+      </c>
+      <c r="C421" t="n">
+        <v>443.35</v>
+      </c>
+      <c r="D421" t="n">
+        <v>445.54</v>
+      </c>
+      <c r="E421" t="n">
+        <v>441.97</v>
+      </c>
+      <c r="F421" t="n">
+        <v>427.23</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>424.33</v>
+      </c>
+      <c r="C422" t="n">
+        <v>440.12</v>
+      </c>
+      <c r="D422" t="n">
+        <v>442.94</v>
+      </c>
+      <c r="E422" t="n">
+        <v>439.12</v>
+      </c>
+      <c r="F422" t="n">
+        <v>426.1</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:12:21+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>425.17</v>
+      </c>
+      <c r="C423" t="n">
+        <v>434.91</v>
+      </c>
+      <c r="D423" t="n">
+        <v>438.12</v>
+      </c>
+      <c r="E423" t="n">
+        <v>435.41</v>
+      </c>
+      <c r="F423" t="n">
+        <v>422.49</v>
+      </c>
+      <c r="G423" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11732,7 +11813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B568"/>
+  <dimension ref="A1:B571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17415,6 +17496,36 @@
       </c>
       <c r="B568" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
@@ -17583,28 +17694,28 @@
         <v>0.0347</v>
       </c>
       <c r="I2" t="n">
-        <v>6.496373956177614</v>
+        <v>6.495086636510418</v>
       </c>
       <c r="J2" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K2" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7921717851845285</v>
+        <v>0.7943431002361042</v>
       </c>
       <c r="M2" t="n">
-        <v>14.90300378022683</v>
+        <v>14.80400808800046</v>
       </c>
       <c r="N2" t="n">
-        <v>599.1898323435157</v>
+        <v>594.8766672279437</v>
       </c>
       <c r="O2" t="n">
-        <v>24.47835436346806</v>
+        <v>24.39009362892942</v>
       </c>
       <c r="P2" t="n">
-        <v>255.1100808936318</v>
+        <v>255.123979790788</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17665,28 +17776,28 @@
         <v>0.0289</v>
       </c>
       <c r="I3" t="n">
-        <v>6.333511840228965</v>
+        <v>6.354474535669262</v>
       </c>
       <c r="J3" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K3" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7216629839987354</v>
+        <v>0.7252868533134387</v>
       </c>
       <c r="M3" t="n">
-        <v>17.76982200937825</v>
+        <v>17.7154597791647</v>
       </c>
       <c r="N3" t="n">
-        <v>831.6713100547563</v>
+        <v>827.5219214515472</v>
       </c>
       <c r="O3" t="n">
-        <v>28.83871200408847</v>
+        <v>28.76668075137532</v>
       </c>
       <c r="P3" t="n">
-        <v>257.3646984641229</v>
+        <v>257.1378715198055</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17747,28 +17858,28 @@
         <v>0.0363</v>
       </c>
       <c r="I4" t="n">
-        <v>5.945306047199948</v>
+        <v>5.970591634867422</v>
       </c>
       <c r="J4" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K4" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8653774536405983</v>
+        <v>0.866928485685427</v>
       </c>
       <c r="M4" t="n">
-        <v>11.78472063871718</v>
+        <v>11.83147415501692</v>
       </c>
       <c r="N4" t="n">
-        <v>296.6696168919463</v>
+        <v>297.1386576979326</v>
       </c>
       <c r="O4" t="n">
-        <v>17.22409988626245</v>
+        <v>17.23771033803308</v>
       </c>
       <c r="P4" t="n">
-        <v>267.0212908396149</v>
+        <v>266.748230698005</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -17829,28 +17940,28 @@
         <v>0.0335</v>
       </c>
       <c r="I5" t="n">
-        <v>5.335270575653115</v>
+        <v>5.356191850416471</v>
       </c>
       <c r="J5" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K5" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8719798560138493</v>
+        <v>0.8734825412467382</v>
       </c>
       <c r="M5" t="n">
-        <v>11.70834497284102</v>
+        <v>11.75587545317805</v>
       </c>
       <c r="N5" t="n">
-        <v>226.1138014451291</v>
+        <v>226.2833526466899</v>
       </c>
       <c r="O5" t="n">
-        <v>15.03708088177786</v>
+        <v>15.04271759512522</v>
       </c>
       <c r="P5" t="n">
-        <v>282.9195050820156</v>
+        <v>282.6939660619091</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -17911,28 +18022,28 @@
         <v>0.0432</v>
       </c>
       <c r="I6" t="n">
-        <v>5.229666433295228</v>
+        <v>5.234337781084271</v>
       </c>
       <c r="J6" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K6" t="n">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8625566045775759</v>
+        <v>0.8643076020388033</v>
       </c>
       <c r="M6" t="n">
-        <v>12.02526433159574</v>
+        <v>11.96150421772943</v>
       </c>
       <c r="N6" t="n">
-        <v>234.6364336263315</v>
+        <v>233.0398886467708</v>
       </c>
       <c r="O6" t="n">
-        <v>15.31784689916737</v>
+        <v>15.26564406262542</v>
       </c>
       <c r="P6" t="n">
-        <v>284.3689173329246</v>
+        <v>284.3181308963938</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -17974,7 +18085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G420"/>
+  <dimension ref="A1:G423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33397,6 +33508,117 @@
         </is>
       </c>
     </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>-36.98028147513989,174.4685354952388</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>-36.979621730887075,174.46813164769588</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>-36.978927620816776,174.46790328834788</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-36.97822119674615,174.46773778911034</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-36.97749089917836,174.46769418783674</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>-36.98027987255269,174.46854368029926</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>-36.979614829176825,174.46816689775156</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>-36.97892206530253,174.4679316627631</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>-36.97821510707635,174.4677688915574</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>-36.977488484677615,174.46770651956683</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:12:21+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>-36.980281667450306,174.46853451303153</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>-36.97960369667502,174.4682237561864</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>-36.97891176621607,174.4679842645521</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>-36.97820717980992,174.46780937929645</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>-36.97748077108708,174.46774591561942</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0187/nzd0187.xlsx
+++ b/data/nzd0187/nzd0187.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G423"/>
+  <dimension ref="A1:G425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11785,7 +11785,7 @@
         <v>425.17</v>
       </c>
       <c r="C423" t="n">
-        <v>434.91</v>
+        <v>435.54</v>
       </c>
       <c r="D423" t="n">
         <v>438.12</v>
@@ -11799,6 +11799,60 @@
       <c r="G423" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>423.17</v>
+      </c>
+      <c r="C424" t="n">
+        <v>430.33</v>
+      </c>
+      <c r="D424" t="n">
+        <v>434.76</v>
+      </c>
+      <c r="E424" t="n">
+        <v>431.86</v>
+      </c>
+      <c r="F424" t="n">
+        <v>422</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:06:10+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>423.35</v>
+      </c>
+      <c r="C425" t="n">
+        <v>431.59</v>
+      </c>
+      <c r="D425" t="n">
+        <v>434.49</v>
+      </c>
+      <c r="E425" t="n">
+        <v>432.6</v>
+      </c>
+      <c r="F425" t="n">
+        <v>422.04</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11813,7 +11867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B571"/>
+  <dimension ref="A1:B573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17526,6 +17580,26 @@
       </c>
       <c r="B571" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>
@@ -17694,28 +17768,28 @@
         <v>0.0347</v>
       </c>
       <c r="I2" t="n">
-        <v>6.495086636510418</v>
+        <v>6.492216773351204</v>
       </c>
       <c r="J2" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="K2" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7943431002361042</v>
+        <v>0.7956649912006681</v>
       </c>
       <c r="M2" t="n">
-        <v>14.80400808800046</v>
+        <v>14.75180405533487</v>
       </c>
       <c r="N2" t="n">
-        <v>594.8766672279437</v>
+        <v>592.0797690951615</v>
       </c>
       <c r="O2" t="n">
-        <v>24.39009362892942</v>
+        <v>24.3326893107844</v>
       </c>
       <c r="P2" t="n">
-        <v>255.123979790788</v>
+        <v>255.1551182594583</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17776,28 +17850,28 @@
         <v>0.0289</v>
       </c>
       <c r="I3" t="n">
-        <v>6.354474535669262</v>
+        <v>6.360236862482821</v>
       </c>
       <c r="J3" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="K3" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7252868533134387</v>
+        <v>0.7274079533913769</v>
       </c>
       <c r="M3" t="n">
-        <v>17.7154597791647</v>
+        <v>17.6512087756391</v>
       </c>
       <c r="N3" t="n">
-        <v>827.5219214515472</v>
+        <v>823.7937661710738</v>
       </c>
       <c r="O3" t="n">
-        <v>28.76668075137532</v>
+        <v>28.70180771608426</v>
       </c>
       <c r="P3" t="n">
-        <v>257.1378715198055</v>
+        <v>257.075188110035</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17858,28 +17932,28 @@
         <v>0.0363</v>
       </c>
       <c r="I4" t="n">
-        <v>5.970591634867422</v>
+        <v>5.979768682891841</v>
       </c>
       <c r="J4" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="K4" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L4" t="n">
-        <v>0.866928485685427</v>
+        <v>0.8681313529543474</v>
       </c>
       <c r="M4" t="n">
-        <v>11.83147415501692</v>
+        <v>11.82356815127927</v>
       </c>
       <c r="N4" t="n">
-        <v>297.1386576979326</v>
+        <v>296.2266754946721</v>
       </c>
       <c r="O4" t="n">
-        <v>17.23771033803308</v>
+        <v>17.21123689612899</v>
       </c>
       <c r="P4" t="n">
-        <v>266.748230698005</v>
+        <v>266.6485919097311</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -17940,28 +18014,28 @@
         <v>0.0335</v>
       </c>
       <c r="I5" t="n">
-        <v>5.356191850416471</v>
+        <v>5.363462583743542</v>
       </c>
       <c r="J5" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="K5" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8734825412467382</v>
+        <v>0.8746259280080385</v>
       </c>
       <c r="M5" t="n">
-        <v>11.75587545317805</v>
+        <v>11.74563664106205</v>
       </c>
       <c r="N5" t="n">
-        <v>226.2833526466899</v>
+        <v>225.5231604200671</v>
       </c>
       <c r="O5" t="n">
-        <v>15.04271759512522</v>
+        <v>15.01742855551732</v>
       </c>
       <c r="P5" t="n">
-        <v>282.6939660619091</v>
+        <v>282.6151561683191</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -18022,28 +18096,28 @@
         <v>0.0432</v>
       </c>
       <c r="I6" t="n">
-        <v>5.234337781084271</v>
+        <v>5.233974307669864</v>
       </c>
       <c r="J6" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="K6" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8643076020388033</v>
+        <v>0.8653470135936677</v>
       </c>
       <c r="M6" t="n">
-        <v>11.96150421772943</v>
+        <v>11.90548321522427</v>
       </c>
       <c r="N6" t="n">
-        <v>233.0398886467708</v>
+        <v>231.909426540002</v>
       </c>
       <c r="O6" t="n">
-        <v>15.26564406262542</v>
+        <v>15.2285727019968</v>
       </c>
       <c r="P6" t="n">
-        <v>284.3181308963938</v>
+        <v>284.3221065940076</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -18085,7 +18159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G423"/>
+  <dimension ref="A1:G425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33595,7 +33669,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>-36.97960369667502,174.4682237561864</t>
+          <t>-36.97960504283308,174.4682168807912</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -33616,6 +33690,80 @@
       <c r="G423" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>-36.98027739388335,174.46855633985868</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>-36.97959391030763,174.46827373921067</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>-36.97890458675631,174.46802093301028</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-36.97819959440746,174.46784812092528</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>-36.97747972408902,174.4677512630054</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:06:10+00:00</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>-36.98027777850454,174.4685543754443</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>-36.97959660262911,174.46825998842368</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>-36.978904009834935,174.46802387958252</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>-36.97820117559096,174.46784004520615</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>-36.97747980955826,174.4677508264841</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0187/nzd0187.xlsx
+++ b/data/nzd0187/nzd0187.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G425"/>
+  <dimension ref="A1:G426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11851,6 +11851,33 @@
         <v>422.04</v>
       </c>
       <c r="G425" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-25 22:11:57+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>420.73</v>
+      </c>
+      <c r="C426" t="n">
+        <v>428.93</v>
+      </c>
+      <c r="D426" t="n">
+        <v>429.61</v>
+      </c>
+      <c r="E426" t="n">
+        <v>427.58</v>
+      </c>
+      <c r="F426" t="n">
+        <v>419.71</v>
+      </c>
+      <c r="G426" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11867,7 +11894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B573"/>
+  <dimension ref="A1:B574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17600,6 +17627,16 @@
       </c>
       <c r="B573" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-02-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>-0.67</v>
       </c>
     </row>
   </sheetData>
@@ -17768,28 +17805,28 @@
         <v>0.0347</v>
       </c>
       <c r="I2" t="n">
-        <v>6.492216773351204</v>
+        <v>6.489602841706093</v>
       </c>
       <c r="J2" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K2" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7956649912006681</v>
+        <v>0.7962426836479727</v>
       </c>
       <c r="M2" t="n">
-        <v>14.75180405533487</v>
+        <v>14.73347431620488</v>
       </c>
       <c r="N2" t="n">
-        <v>592.0797690951615</v>
+        <v>590.7496797344432</v>
       </c>
       <c r="O2" t="n">
-        <v>24.3326893107844</v>
+        <v>24.30534261709641</v>
       </c>
       <c r="P2" t="n">
-        <v>255.1551182594583</v>
+        <v>255.1835216816882</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17850,28 +17887,28 @@
         <v>0.0289</v>
       </c>
       <c r="I3" t="n">
-        <v>6.360236862482821</v>
+        <v>6.361941288362699</v>
       </c>
       <c r="J3" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K3" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7274079533913769</v>
+        <v>0.7284012417570815</v>
       </c>
       <c r="M3" t="n">
-        <v>17.6512087756391</v>
+        <v>17.61519435510165</v>
       </c>
       <c r="N3" t="n">
-        <v>823.7937661710738</v>
+        <v>821.8719206638623</v>
       </c>
       <c r="O3" t="n">
-        <v>28.70180771608426</v>
+        <v>28.66830864672456</v>
       </c>
       <c r="P3" t="n">
-        <v>257.075188110035</v>
+        <v>257.0566175290046</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17932,28 +17969,28 @@
         <v>0.0363</v>
       </c>
       <c r="I4" t="n">
-        <v>5.979768682891841</v>
+        <v>5.981979864613925</v>
       </c>
       <c r="J4" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K4" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8681313529543474</v>
+        <v>0.8687084353787464</v>
       </c>
       <c r="M4" t="n">
-        <v>11.82356815127927</v>
+        <v>11.80708727244799</v>
       </c>
       <c r="N4" t="n">
-        <v>296.2266754946721</v>
+        <v>295.5821553786072</v>
       </c>
       <c r="O4" t="n">
-        <v>17.21123689612899</v>
+        <v>17.1925028829024</v>
       </c>
       <c r="P4" t="n">
-        <v>266.6485919097311</v>
+        <v>266.6245489067996</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -18014,28 +18051,28 @@
         <v>0.0335</v>
       </c>
       <c r="I5" t="n">
-        <v>5.363462583743542</v>
+        <v>5.364911920747375</v>
       </c>
       <c r="J5" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K5" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8746259280080385</v>
+        <v>0.875165705818275</v>
       </c>
       <c r="M5" t="n">
-        <v>11.74563664106205</v>
+        <v>11.7268604719739</v>
       </c>
       <c r="N5" t="n">
-        <v>225.5231604200671</v>
+        <v>225.0129763583861</v>
       </c>
       <c r="O5" t="n">
-        <v>15.01742855551732</v>
+        <v>15.0004325390432</v>
       </c>
       <c r="P5" t="n">
-        <v>282.6151561683191</v>
+        <v>282.5994236109116</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -18096,28 +18133,28 @@
         <v>0.0432</v>
       </c>
       <c r="I6" t="n">
-        <v>5.233974307669864</v>
+        <v>5.232700279566049</v>
       </c>
       <c r="J6" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K6" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8653470135936677</v>
+        <v>0.8658018047967784</v>
       </c>
       <c r="M6" t="n">
-        <v>11.90548321522427</v>
+        <v>11.8837878461417</v>
       </c>
       <c r="N6" t="n">
-        <v>231.909426540002</v>
+        <v>231.3676068209808</v>
       </c>
       <c r="O6" t="n">
-        <v>15.2285727019968</v>
+        <v>15.21077272267851</v>
       </c>
       <c r="P6" t="n">
-        <v>284.3221065940076</v>
+        <v>284.336062014977</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -18159,7 +18196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G425"/>
+  <dimension ref="A1:G426"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33767,6 +33804,43 @@
         </is>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-25 22:11:57+00:00</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>-36.9802721801263,174.46858296858431</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>-36.979590918837474,174.46828901786168</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>-36.97889358250308,174.468077136139</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-36.97819044917322,174.46789482913178</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>-36.977474830972554,174.46777625384811</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0187/nzd0187.xlsx
+++ b/data/nzd0187/nzd0187.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G426"/>
+  <dimension ref="A1:G427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11866,7 +11866,7 @@
         <v>420.73</v>
       </c>
       <c r="C426" t="n">
-        <v>428.93</v>
+        <v>426.63</v>
       </c>
       <c r="D426" t="n">
         <v>429.61</v>
@@ -11880,6 +11880,33 @@
       <c r="G426" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>420.2</v>
+      </c>
+      <c r="C427" t="n">
+        <v>425.69</v>
+      </c>
+      <c r="D427" t="n">
+        <v>428.3</v>
+      </c>
+      <c r="E427" t="n">
+        <v>426.57</v>
+      </c>
+      <c r="F427" t="n">
+        <v>419.94</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B574"/>
+  <dimension ref="A1:B575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17637,6 +17664,16 @@
       </c>
       <c r="B574" t="n">
         <v>-0.67</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>-0.39</v>
       </c>
     </row>
   </sheetData>
@@ -17805,28 +17842,28 @@
         <v>0.0347</v>
       </c>
       <c r="I2" t="n">
-        <v>6.489602841706093</v>
+        <v>6.48678448048089</v>
       </c>
       <c r="J2" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K2" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7962426836479727</v>
+        <v>0.7967985311718166</v>
       </c>
       <c r="M2" t="n">
-        <v>14.73347431620488</v>
+        <v>14.7165794246186</v>
       </c>
       <c r="N2" t="n">
-        <v>590.7496797344432</v>
+        <v>589.4406592689305</v>
       </c>
       <c r="O2" t="n">
-        <v>24.30534261709641</v>
+        <v>24.27839902606699</v>
       </c>
       <c r="P2" t="n">
-        <v>255.1835216816882</v>
+        <v>255.2141505779381</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17887,28 +17924,28 @@
         <v>0.0289</v>
       </c>
       <c r="I3" t="n">
-        <v>6.361941288362699</v>
+        <v>6.361180528098708</v>
       </c>
       <c r="J3" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K3" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7284012417570815</v>
+        <v>0.7292467217765872</v>
       </c>
       <c r="M3" t="n">
-        <v>17.61519435510165</v>
+        <v>17.57081919353505</v>
       </c>
       <c r="N3" t="n">
-        <v>821.8719206638623</v>
+        <v>819.8959847072325</v>
       </c>
       <c r="O3" t="n">
-        <v>28.66830864672456</v>
+        <v>28.6338258831619</v>
       </c>
       <c r="P3" t="n">
-        <v>257.0566175290046</v>
+        <v>257.0649060251004</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -17969,28 +18006,28 @@
         <v>0.0363</v>
       </c>
       <c r="I4" t="n">
-        <v>5.981979864613925</v>
+        <v>5.983581636992897</v>
       </c>
       <c r="J4" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K4" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8687084353787464</v>
+        <v>0.8692663976324941</v>
       </c>
       <c r="M4" t="n">
-        <v>11.80708727244799</v>
+        <v>11.78749154702592</v>
       </c>
       <c r="N4" t="n">
-        <v>295.5821553786072</v>
+        <v>294.9130772076355</v>
       </c>
       <c r="O4" t="n">
-        <v>17.1925028829024</v>
+        <v>17.17303343057468</v>
       </c>
       <c r="P4" t="n">
-        <v>266.6245489067996</v>
+        <v>266.6071299194448</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -18051,28 +18088,28 @@
         <v>0.0335</v>
       </c>
       <c r="I5" t="n">
-        <v>5.364911920747375</v>
+        <v>5.365895409722908</v>
       </c>
       <c r="J5" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K5" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L5" t="n">
-        <v>0.875165705818275</v>
+        <v>0.8756869095033792</v>
       </c>
       <c r="M5" t="n">
-        <v>11.7268604719739</v>
+        <v>11.70524613428125</v>
       </c>
       <c r="N5" t="n">
-        <v>225.0129763583861</v>
+        <v>224.4916400152601</v>
       </c>
       <c r="O5" t="n">
-        <v>15.0004325390432</v>
+        <v>14.98304508487043</v>
       </c>
       <c r="P5" t="n">
-        <v>282.5994236109116</v>
+        <v>282.5887464091473</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -18133,28 +18170,28 @@
         <v>0.0432</v>
       </c>
       <c r="I6" t="n">
-        <v>5.232700279566049</v>
+        <v>5.231538877987298</v>
       </c>
       <c r="J6" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K6" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8658018047967784</v>
+        <v>0.8662573047863565</v>
       </c>
       <c r="M6" t="n">
-        <v>11.8837878461417</v>
+        <v>11.86156685565617</v>
       </c>
       <c r="N6" t="n">
-        <v>231.3676068209808</v>
+        <v>230.8253001786866</v>
       </c>
       <c r="O6" t="n">
-        <v>15.21077272267851</v>
+        <v>15.19293586436429</v>
       </c>
       <c r="P6" t="n">
-        <v>284.336062014977</v>
+        <v>284.3487854758476</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -18196,7 +18233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G426"/>
+  <dimension ref="A1:G427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33817,7 +33854,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>-36.979590918837474,174.46828901786168</t>
+          <t>-36.97958600427514,174.46831411849993</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -33838,6 +33875,43 @@
       <c r="G426" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>-36.98027104762912,174.46858875269223</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>-36.97958399571337,174.46832437702065</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>-36.97889078335875,174.46809143246608</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-36.97818829106623,174.46790585139374</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>-36.977475322421164,174.46777374385093</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0187/nzd0187.xlsx
+++ b/data/nzd0187/nzd0187.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G427"/>
+  <dimension ref="A1:G429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11905,6 +11905,60 @@
         <v>419.94</v>
       </c>
       <c r="G427" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:58+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>420.79</v>
+      </c>
+      <c r="C428" t="n">
+        <v>421.95</v>
+      </c>
+      <c r="D428" t="n">
+        <v>425.63</v>
+      </c>
+      <c r="E428" t="n">
+        <v>424.96</v>
+      </c>
+      <c r="F428" t="n">
+        <v>419.41</v>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>420.23</v>
+      </c>
+      <c r="C429" t="n">
+        <v>422.28</v>
+      </c>
+      <c r="D429" t="n">
+        <v>425.14</v>
+      </c>
+      <c r="E429" t="n">
+        <v>424.39</v>
+      </c>
+      <c r="F429" t="n">
+        <v>418.04</v>
+      </c>
+      <c r="G429" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11921,7 +11975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B575"/>
+  <dimension ref="A1:B577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17674,6 +17728,26 @@
       </c>
       <c r="B575" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>0.91</v>
       </c>
     </row>
   </sheetData>
@@ -17842,28 +17916,28 @@
         <v>0.0347</v>
       </c>
       <c r="I2" t="n">
-        <v>6.48678448048089</v>
+        <v>6.480927752237162</v>
       </c>
       <c r="J2" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K2" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7967985311718166</v>
+        <v>0.7978986825379539</v>
       </c>
       <c r="M2" t="n">
-        <v>14.7165794246186</v>
+        <v>14.68489520113877</v>
       </c>
       <c r="N2" t="n">
-        <v>589.4406592689305</v>
+        <v>586.8580874089702</v>
       </c>
       <c r="O2" t="n">
-        <v>24.27839902606699</v>
+        <v>24.22515402239932</v>
       </c>
       <c r="P2" t="n">
-        <v>255.2141505779381</v>
+        <v>255.2781094868559</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17924,28 +17998,28 @@
         <v>0.0289</v>
       </c>
       <c r="I3" t="n">
-        <v>6.361180528098708</v>
+        <v>6.358009736186311</v>
       </c>
       <c r="J3" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K3" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7292467217765872</v>
+        <v>0.7308116458030193</v>
       </c>
       <c r="M3" t="n">
-        <v>17.57081919353505</v>
+        <v>17.51079162649371</v>
       </c>
       <c r="N3" t="n">
-        <v>819.8959847072325</v>
+        <v>816.0894288791636</v>
       </c>
       <c r="O3" t="n">
-        <v>28.6338258831619</v>
+        <v>28.56727898976666</v>
       </c>
       <c r="P3" t="n">
-        <v>257.0649060251004</v>
+        <v>257.0996209852407</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -18006,28 +18080,28 @@
         <v>0.0363</v>
       </c>
       <c r="I4" t="n">
-        <v>5.983581636992897</v>
+        <v>5.983690498199207</v>
       </c>
       <c r="J4" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K4" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8692663976324941</v>
+        <v>0.8702884443460739</v>
       </c>
       <c r="M4" t="n">
-        <v>11.78749154702592</v>
+        <v>11.7339884881844</v>
       </c>
       <c r="N4" t="n">
-        <v>294.9130772076355</v>
+        <v>293.5230010875765</v>
       </c>
       <c r="O4" t="n">
-        <v>17.17303343057468</v>
+        <v>17.13251298226785</v>
       </c>
       <c r="P4" t="n">
-        <v>266.6071299194448</v>
+        <v>266.6059475999355</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -18088,28 +18162,28 @@
         <v>0.0335</v>
       </c>
       <c r="I5" t="n">
-        <v>5.365895409722908</v>
+        <v>5.365729216999944</v>
       </c>
       <c r="J5" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K5" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8756869095033792</v>
+        <v>0.8766536868166227</v>
       </c>
       <c r="M5" t="n">
-        <v>11.70524613428125</v>
+        <v>11.65209919620771</v>
       </c>
       <c r="N5" t="n">
-        <v>224.4916400152601</v>
+        <v>223.433915720966</v>
       </c>
       <c r="O5" t="n">
-        <v>14.98304508487043</v>
+        <v>14.94770603540777</v>
       </c>
       <c r="P5" t="n">
-        <v>282.5887464091473</v>
+        <v>282.5905666070317</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -18170,28 +18244,28 @@
         <v>0.0432</v>
       </c>
       <c r="I6" t="n">
-        <v>5.231538877987298</v>
+        <v>5.227720635860421</v>
       </c>
       <c r="J6" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K6" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8662573047863565</v>
+        <v>0.8670741001940535</v>
       </c>
       <c r="M6" t="n">
-        <v>11.86156685565617</v>
+        <v>11.82556581683017</v>
       </c>
       <c r="N6" t="n">
-        <v>230.8253001786866</v>
+        <v>229.8081598610877</v>
       </c>
       <c r="O6" t="n">
-        <v>15.19293586436429</v>
+        <v>15.15942478661667</v>
       </c>
       <c r="P6" t="n">
-        <v>284.3487854758476</v>
+        <v>284.3908302661586</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -18233,7 +18307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G427"/>
+  <dimension ref="A1:G429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33915,6 +33989,80 @@
         </is>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:58+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>-36.98027230833351,174.46858231377965</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>-36.979576004192985,174.46836519283153</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>-36.97888507822725,174.4681205707782</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-36.97818485091339,174.46792342153276</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>-36.97747418995254,174.46777952775736</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>-36.98027111173273,174.4685884252899</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>-36.979576709327695,174.4683615914368</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>-36.97888403121733,174.4681259182582</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>-36.978183632970484,174.46792964201637</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>-36.97747126262669,174.467794478609</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0187/nzd0187.xlsx
+++ b/data/nzd0187/nzd0187.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G429"/>
+  <dimension ref="A1:G435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11959,6 +11959,168 @@
         <v>418.04</v>
       </c>
       <c r="G429" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>420.47</v>
+      </c>
+      <c r="C430" t="n">
+        <v>423.01</v>
+      </c>
+      <c r="D430" t="n">
+        <v>425.67</v>
+      </c>
+      <c r="E430" t="n">
+        <v>424.11</v>
+      </c>
+      <c r="F430" t="n">
+        <v>418.92</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>421.43</v>
+      </c>
+      <c r="C431" t="n">
+        <v>424.99</v>
+      </c>
+      <c r="D431" t="n">
+        <v>427.23</v>
+      </c>
+      <c r="E431" t="n">
+        <v>425.39</v>
+      </c>
+      <c r="F431" t="n">
+        <v>418.57</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>421.53</v>
+      </c>
+      <c r="C432" t="n">
+        <v>426.42</v>
+      </c>
+      <c r="D432" t="n">
+        <v>428.64</v>
+      </c>
+      <c r="E432" t="n">
+        <v>426.47</v>
+      </c>
+      <c r="F432" t="n">
+        <v>418.9</v>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>418.61</v>
+      </c>
+      <c r="C433" t="n">
+        <v>426.42</v>
+      </c>
+      <c r="D433" t="n">
+        <v>426.19</v>
+      </c>
+      <c r="E433" t="n">
+        <v>423.23</v>
+      </c>
+      <c r="F433" t="n">
+        <v>417.37</v>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>419.52</v>
+      </c>
+      <c r="C434" t="n">
+        <v>428.14</v>
+      </c>
+      <c r="D434" t="n">
+        <v>427.4</v>
+      </c>
+      <c r="E434" t="n">
+        <v>424.76</v>
+      </c>
+      <c r="F434" t="n">
+        <v>418.02</v>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>419.93</v>
+      </c>
+      <c r="C435" t="n">
+        <v>429.92</v>
+      </c>
+      <c r="D435" t="n">
+        <v>428.7</v>
+      </c>
+      <c r="E435" t="n">
+        <v>426.24</v>
+      </c>
+      <c r="F435" t="n">
+        <v>418.93</v>
+      </c>
+      <c r="G435" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11975,7 +12137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B577"/>
+  <dimension ref="A1:B583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17748,6 +17910,66 @@
       </c>
       <c r="B577" t="n">
         <v>0.91</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>
@@ -17916,28 +18138,28 @@
         <v>0.0347</v>
       </c>
       <c r="I2" t="n">
-        <v>6.480927752237162</v>
+        <v>6.461978289407738</v>
       </c>
       <c r="J2" t="n">
+        <v>434</v>
+      </c>
+      <c r="K2" t="n">
         <v>428</v>
       </c>
-      <c r="K2" t="n">
-        <v>422</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.7978986825379539</v>
+        <v>0.8009837679823089</v>
       </c>
       <c r="M2" t="n">
-        <v>14.68489520113877</v>
+        <v>14.60084751945924</v>
       </c>
       <c r="N2" t="n">
-        <v>586.8580874089702</v>
+        <v>579.3976294095798</v>
       </c>
       <c r="O2" t="n">
-        <v>24.22515402239932</v>
+        <v>24.07067987011542</v>
       </c>
       <c r="P2" t="n">
-        <v>255.2781094868559</v>
+        <v>255.4859570992385</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -17998,28 +18220,28 @@
         <v>0.0289</v>
       </c>
       <c r="I3" t="n">
-        <v>6.358009736186311</v>
+        <v>6.358599342269951</v>
       </c>
       <c r="J3" t="n">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="K3" t="n">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7308116458030193</v>
+        <v>0.7360207839958133</v>
       </c>
       <c r="M3" t="n">
-        <v>17.51079162649371</v>
+        <v>17.2879712275049</v>
       </c>
       <c r="N3" t="n">
-        <v>816.0894288791636</v>
+        <v>804.7614568227671</v>
       </c>
       <c r="O3" t="n">
-        <v>28.56727898976666</v>
+        <v>28.3683178356202</v>
       </c>
       <c r="P3" t="n">
-        <v>257.0996209852407</v>
+        <v>257.0930747167415</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -18080,28 +18302,28 @@
         <v>0.0363</v>
       </c>
       <c r="I4" t="n">
-        <v>5.983690498199207</v>
+        <v>5.987501242521238</v>
       </c>
       <c r="J4" t="n">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="K4" t="n">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8702884443460739</v>
+        <v>0.8733706100130572</v>
       </c>
       <c r="M4" t="n">
-        <v>11.7339884881844</v>
+        <v>11.5896887078106</v>
       </c>
       <c r="N4" t="n">
-        <v>293.5230010875765</v>
+        <v>289.4733822176328</v>
       </c>
       <c r="O4" t="n">
-        <v>17.13251298226785</v>
+        <v>17.01391730959196</v>
       </c>
       <c r="P4" t="n">
-        <v>266.6059475999355</v>
+        <v>266.5641166019849</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -18162,28 +18384,28 @@
         <v>0.0335</v>
       </c>
       <c r="I5" t="n">
-        <v>5.365729216999944</v>
+        <v>5.364931746638304</v>
       </c>
       <c r="J5" t="n">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="K5" t="n">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8766536868166227</v>
+        <v>0.8794427890452755</v>
       </c>
       <c r="M5" t="n">
-        <v>11.65209919620771</v>
+        <v>11.50282655952151</v>
       </c>
       <c r="N5" t="n">
-        <v>223.433915720966</v>
+        <v>220.3355354957513</v>
       </c>
       <c r="O5" t="n">
-        <v>14.94770603540777</v>
+        <v>14.84370356399478</v>
       </c>
       <c r="P5" t="n">
-        <v>282.5905666070317</v>
+        <v>282.5993029164342</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -18244,28 +18466,28 @@
         <v>0.0432</v>
       </c>
       <c r="I6" t="n">
-        <v>5.227720635860421</v>
+        <v>5.21485587584492</v>
       </c>
       <c r="J6" t="n">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="K6" t="n">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8670741001940535</v>
+        <v>0.8693421419056679</v>
       </c>
       <c r="M6" t="n">
-        <v>11.82556581683017</v>
+        <v>11.72703158926389</v>
       </c>
       <c r="N6" t="n">
-        <v>229.8081598610877</v>
+        <v>226.891314809044</v>
       </c>
       <c r="O6" t="n">
-        <v>15.15942478661667</v>
+        <v>15.06291189674307</v>
       </c>
       <c r="P6" t="n">
-        <v>284.3908302661586</v>
+        <v>284.5330849731891</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -18307,7 +18529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G429"/>
+  <dimension ref="A1:G435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34063,6 +34285,228 @@
         </is>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>-36.98027162456168,174.46858580607125</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>-36.97957826917077,174.46835362471492</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>-36.97888516369744,174.4681201342492</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-36.978183034682594,174.46793269769245</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-36.977473142952995,174.4677848751424</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>-36.98027367587688,174.4685753291962</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>-36.979582499975315,174.46833201634422</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>-36.97888849703349,174.4681031096179</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-36.978185769712226,174.4679187288871</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>-36.977472395096044,174.46778869470305</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>-36.98027388955549,174.468574237855</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>-36.97958555555397,174.46831641029715</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>-36.9788915098544,174.46808772196908</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-36.97818807739222,174.4679069427068</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>-36.97747310021832,174.467785093403</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>-36.98026765013587,174.46860610501497</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>-36.97958555555397,174.46831641029715</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>-36.97888627480974,174.4681144593723</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-36.97818115434879,174.46794230124553</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-36.9774698310141,174.4678017903389</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>-36.98026959461344,174.4685961738116</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>-36.97958923079274,174.46829763938564</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>-36.978888860281515,174.46810125436954</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-36.97818442356503,174.46792560415864</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>-36.977471219891996,174.46779469686956</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>-36.980270470696475,174.4685916993132</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>-36.979593034234426,174.4682782136729</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>-36.978891638059494,174.46808706717545</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>-36.97818758594194,174.46790945272673</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>-36.97747316432034,174.4677847660121</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0187/nzd0187.xlsx
+++ b/data/nzd0187/nzd0187.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G435"/>
+  <dimension ref="A1:G439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12123,6 +12123,114 @@
       <c r="G435" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:11:18+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>419.31</v>
+      </c>
+      <c r="C436" t="n">
+        <v>428.77</v>
+      </c>
+      <c r="D436" t="n">
+        <v>428.67</v>
+      </c>
+      <c r="E436" t="n">
+        <v>426.12</v>
+      </c>
+      <c r="F436" t="n">
+        <v>419.64</v>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:11:18+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>417.84</v>
+      </c>
+      <c r="C437" t="n">
+        <v>428.34</v>
+      </c>
+      <c r="D437" t="n">
+        <v>428</v>
+      </c>
+      <c r="E437" t="n">
+        <v>426.02</v>
+      </c>
+      <c r="F437" t="n">
+        <v>418.22</v>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>417.29</v>
+      </c>
+      <c r="C438" t="n">
+        <v>427.28</v>
+      </c>
+      <c r="D438" t="n">
+        <v>427.74</v>
+      </c>
+      <c r="E438" t="n">
+        <v>425.83</v>
+      </c>
+      <c r="F438" t="n">
+        <v>418.11</v>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>417.88</v>
+      </c>
+      <c r="C439" t="n">
+        <v>427.71</v>
+      </c>
+      <c r="D439" t="n">
+        <v>428.12</v>
+      </c>
+      <c r="E439" t="n">
+        <v>426.78</v>
+      </c>
+      <c r="F439" t="n">
+        <v>419.52</v>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12137,7 +12245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B583"/>
+  <dimension ref="A1:B588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17970,6 +18078,56 @@
       </c>
       <c r="B583" t="n">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -18138,28 +18296,28 @@
         <v>0.0347</v>
       </c>
       <c r="I2" t="n">
-        <v>6.461978289407738</v>
+        <v>6.445491519882997</v>
       </c>
       <c r="J2" t="n">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="K2" t="n">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8009837679823089</v>
+        <v>0.802647921605079</v>
       </c>
       <c r="M2" t="n">
-        <v>14.60084751945924</v>
+        <v>14.57343854506646</v>
       </c>
       <c r="N2" t="n">
-        <v>579.3976294095798</v>
+        <v>574.924932441619</v>
       </c>
       <c r="O2" t="n">
-        <v>24.07067987011542</v>
+        <v>23.97759229867793</v>
       </c>
       <c r="P2" t="n">
-        <v>255.4859570992385</v>
+        <v>255.6675826565939</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -18220,28 +18378,28 @@
         <v>0.0289</v>
       </c>
       <c r="I3" t="n">
-        <v>6.358599342269951</v>
+        <v>6.360586848151138</v>
       </c>
       <c r="J3" t="n">
+        <v>438</v>
+      </c>
+      <c r="K3" t="n">
         <v>434</v>
       </c>
-      <c r="K3" t="n">
-        <v>430</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.7360207839958133</v>
+        <v>0.7394664410460043</v>
       </c>
       <c r="M3" t="n">
-        <v>17.2879712275049</v>
+        <v>17.13569555527978</v>
       </c>
       <c r="N3" t="n">
-        <v>804.7614568227671</v>
+        <v>797.3615290375578</v>
       </c>
       <c r="O3" t="n">
-        <v>28.3683178356202</v>
+        <v>28.23759070879734</v>
       </c>
       <c r="P3" t="n">
-        <v>257.0930747167415</v>
+        <v>257.0711386705448</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -18302,28 +18460,28 @@
         <v>0.0363</v>
       </c>
       <c r="I4" t="n">
-        <v>5.987501242521238</v>
+        <v>5.990385497337986</v>
       </c>
       <c r="J4" t="n">
+        <v>438</v>
+      </c>
+      <c r="K4" t="n">
         <v>434</v>
       </c>
-      <c r="K4" t="n">
-        <v>430</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.8733706100130572</v>
+        <v>0.8753510768523062</v>
       </c>
       <c r="M4" t="n">
-        <v>11.5896887078106</v>
+        <v>11.49738900312582</v>
       </c>
       <c r="N4" t="n">
-        <v>289.4733822176328</v>
+        <v>286.8343533075252</v>
       </c>
       <c r="O4" t="n">
-        <v>17.01391730959196</v>
+        <v>16.93618473291801</v>
       </c>
       <c r="P4" t="n">
-        <v>266.5641166019849</v>
+        <v>266.5323361935725</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -18384,28 +18542,28 @@
         <v>0.0335</v>
       </c>
       <c r="I5" t="n">
-        <v>5.364931746638304</v>
+        <v>5.365550161647275</v>
       </c>
       <c r="J5" t="n">
+        <v>438</v>
+      </c>
+      <c r="K5" t="n">
         <v>434</v>
       </c>
-      <c r="K5" t="n">
-        <v>430</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.8794427890452755</v>
+        <v>0.8812715823973031</v>
       </c>
       <c r="M5" t="n">
-        <v>11.50282655952151</v>
+        <v>11.40081371340598</v>
       </c>
       <c r="N5" t="n">
-        <v>220.3355354957513</v>
+        <v>218.3070005597156</v>
       </c>
       <c r="O5" t="n">
-        <v>14.84370356399478</v>
+        <v>14.77521575340663</v>
       </c>
       <c r="P5" t="n">
-        <v>282.5993029164342</v>
+        <v>282.5924976519944</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -18466,28 +18624,28 @@
         <v>0.0432</v>
       </c>
       <c r="I6" t="n">
-        <v>5.21485587584492</v>
+        <v>5.206688899607859</v>
       </c>
       <c r="J6" t="n">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="K6" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8693421419056679</v>
+        <v>0.8708037965797921</v>
       </c>
       <c r="M6" t="n">
-        <v>11.72703158926389</v>
+        <v>11.66079251503455</v>
       </c>
       <c r="N6" t="n">
-        <v>226.891314809044</v>
+        <v>224.9831295132049</v>
       </c>
       <c r="O6" t="n">
-        <v>15.06291189674307</v>
+        <v>14.99943763989853</v>
       </c>
       <c r="P6" t="n">
-        <v>284.5330849731891</v>
+        <v>284.6237942840613</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -18529,7 +18687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G435"/>
+  <dimension ref="A1:G439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34507,6 +34665,154 @@
         </is>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:11:18+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>-36.98026914588792,174.4685984656278</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>-36.97959057695505,174.46829076399314</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>-36.978891573956936,174.46808739457228</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-36.97818732953309,174.46791076230235</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>-36.977474681401226,174.46777701776026</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:11:18+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>-36.980266004808044,174.46861450834047</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>-36.979589658145905,174.4682954567214</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>-36.97889014233308,174.46809470643396</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-36.978187115859015,174.46791185361536</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>-36.97747164723894,174.46779251426358</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>-36.98026482957354,174.4686205107156</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>-36.97958739317372,174.4683070248416</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>-36.978889586777456,174.46809754387274</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-36.97818670987829,174.46791392711003</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>-36.97747141219813,174.46779371469688</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>-36.980266090279635,174.46861407180407</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>-36.979588311983335,174.4683023321137</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>-36.97889039874337,174.4680933968468</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>-36.97818873978163,174.46790355963637</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>-36.977474424993225,174.46777832732397</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
